--- a/template_trouble.xlsx
+++ b/template_trouble.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\APT\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\APT\Desktop\点検表　アプリ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BFF65C5-FB59-4EB5-B5B1-EB67E40CC190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309DAA05-832A-4B60-9ED0-A066840613C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="420" windowWidth="15405" windowHeight="8055" tabRatio="715" xr2:uid="{794F5D1F-34A6-47D1-A373-B12AD81C5BED}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="715" xr2:uid="{794F5D1F-34A6-47D1-A373-B12AD81C5BED}"/>
   </bookViews>
   <sheets>
     <sheet name="作業報告書" sheetId="25" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>作成</t>
     <rPh sb="0" eb="2">
@@ -223,6 +223,40 @@
   <si>
     <t>トラブル</t>
   </si>
+  <si>
+    <t>状況写真①</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シャシン1</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>状況写真②</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウキョウシャシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処置前</t>
+    <rPh sb="0" eb="2">
+      <t>ショチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>処置後</t>
+    <rPh sb="0" eb="3">
+      <t>ショチゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1271,6 +1305,69 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1289,27 +1386,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1329,9 +1408,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1363,48 +1439,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1782,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5722521-1D67-485A-A505-AE810D283E2A}">
-  <dimension ref="A1:BT69"/>
+  <dimension ref="A1:BT67"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="76" width="3.625" style="1" customWidth="1"/>
@@ -1791,19 +1825,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="67"/>
-      <c r="F1" s="68" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="88"/>
+      <c r="F1" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
       <c r="K1" s="58" t="s">
         <v>2</v>
       </c>
@@ -1813,19 +1847,19 @@
       <c r="O1" s="58"/>
       <c r="P1" s="58"/>
       <c r="Q1" s="2"/>
-      <c r="AK1" s="65" t="s">
+      <c r="AK1" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="66"/>
-      <c r="AM1" s="66"/>
-      <c r="AN1" s="67"/>
-      <c r="AP1" s="68" t="s">
+      <c r="AL1" s="87"/>
+      <c r="AM1" s="87"/>
+      <c r="AN1" s="88"/>
+      <c r="AP1" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="AQ1" s="68"/>
-      <c r="AR1" s="68"/>
-      <c r="AS1" s="68"/>
-      <c r="AT1" s="68"/>
+      <c r="AQ1" s="89"/>
+      <c r="AR1" s="89"/>
+      <c r="AS1" s="89"/>
+      <c r="AT1" s="89"/>
       <c r="AU1" s="58" t="s">
         <v>2</v>
       </c>
@@ -1841,11 +1875,11 @@
       <c r="B2" s="61"/>
       <c r="C2" s="61"/>
       <c r="D2" s="62"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
       <c r="K2" s="59"/>
       <c r="L2" s="59"/>
       <c r="M2" s="59"/>
@@ -1873,11 +1907,11 @@
       <c r="AM2" s="61"/>
       <c r="AN2" s="62"/>
       <c r="AO2" s="20"/>
-      <c r="AP2" s="69"/>
-      <c r="AQ2" s="69"/>
-      <c r="AR2" s="69"/>
-      <c r="AS2" s="69"/>
-      <c r="AT2" s="69"/>
+      <c r="AP2" s="90"/>
+      <c r="AQ2" s="90"/>
+      <c r="AR2" s="90"/>
+      <c r="AS2" s="90"/>
+      <c r="AT2" s="90"/>
       <c r="AU2" s="59"/>
       <c r="AV2" s="59"/>
       <c r="AW2" s="59"/>
@@ -1911,41 +1945,41 @@
       <c r="BT2" s="64"/>
     </row>
     <row r="3" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="104"/>
-      <c r="D3" s="104"/>
-      <c r="E3" s="104"/>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="104"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="104"/>
-      <c r="P3" s="104"/>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="104"/>
-      <c r="S3" s="104"/>
-      <c r="T3" s="104"/>
-      <c r="U3" s="105"/>
-      <c r="V3" s="106" t="s">
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="W3" s="104"/>
-      <c r="X3" s="104"/>
-      <c r="Y3" s="104"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
       <c r="Z3" s="112"/>
       <c r="AA3" s="26" t="s">
         <v>0</v>
       </c>
       <c r="AB3" s="110"/>
-      <c r="AC3" s="70"/>
+      <c r="AC3" s="91"/>
       <c r="AD3" s="27"/>
       <c r="AE3" s="27"/>
       <c r="AF3" s="27"/>
@@ -1993,33 +2027,33 @@
       <c r="BT3" s="28"/>
     </row>
     <row r="4" spans="1:72" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="76"/>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="97"/>
-      <c r="V4" s="98"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="69"/>
+      <c r="S4" s="69"/>
+      <c r="T4" s="69"/>
+      <c r="U4" s="70"/>
+      <c r="V4" s="71"/>
       <c r="W4" s="33"/>
       <c r="X4" s="33"/>
       <c r="Y4" s="33"/>
-      <c r="Z4" s="101"/>
-      <c r="AA4" s="102"/>
+      <c r="Z4" s="74"/>
+      <c r="AA4" s="75"/>
       <c r="AB4" s="37"/>
       <c r="AC4" s="35"/>
       <c r="AD4" s="36"/>
@@ -2028,7 +2062,7 @@
       <c r="AG4" s="36"/>
       <c r="AH4" s="36"/>
       <c r="AI4" s="36"/>
-      <c r="AJ4" s="71"/>
+      <c r="AJ4" s="76"/>
       <c r="AK4" s="29"/>
       <c r="AL4" s="30"/>
       <c r="AM4" s="30"/>
@@ -2067,34 +2101,34 @@
       <c r="BT4" s="31"/>
     </row>
     <row r="5" spans="1:72" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="76" t="s">
+      <c r="A5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="97"/>
-      <c r="V5" s="102"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="70"/>
+      <c r="V5" s="75"/>
       <c r="W5" s="36"/>
       <c r="X5" s="36"/>
       <c r="Y5" s="36"/>
-      <c r="Z5" s="71"/>
+      <c r="Z5" s="76"/>
       <c r="AA5" s="111"/>
       <c r="AB5" s="40"/>
       <c r="AC5" s="38"/>
@@ -2104,7 +2138,7 @@
       <c r="AG5" s="39"/>
       <c r="AH5" s="39"/>
       <c r="AI5" s="39"/>
-      <c r="AJ5" s="72"/>
+      <c r="AJ5" s="92"/>
       <c r="AK5" s="4"/>
       <c r="AL5" s="7"/>
       <c r="AM5" s="8"/>
@@ -2143,44 +2177,44 @@
       <c r="BT5" s="6"/>
     </row>
     <row r="6" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="76"/>
-      <c r="B6" s="77"/>
-      <c r="C6" s="77"/>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77"/>
-      <c r="G6" s="77"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="77"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77"/>
-      <c r="T6" s="77"/>
-      <c r="U6" s="97"/>
-      <c r="V6" s="102"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="69"/>
+      <c r="U6" s="70"/>
+      <c r="V6" s="75"/>
       <c r="W6" s="36"/>
       <c r="X6" s="36"/>
       <c r="Y6" s="36"/>
-      <c r="Z6" s="71"/>
-      <c r="AA6" s="76" t="s">
+      <c r="Z6" s="76"/>
+      <c r="AA6" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="AB6" s="77"/>
-      <c r="AC6" s="77"/>
-      <c r="AD6" s="77"/>
-      <c r="AE6" s="77"/>
-      <c r="AF6" s="77"/>
-      <c r="AG6" s="77"/>
-      <c r="AH6" s="77"/>
-      <c r="AI6" s="77"/>
-      <c r="AJ6" s="78"/>
+      <c r="AB6" s="69"/>
+      <c r="AC6" s="69"/>
+      <c r="AD6" s="69"/>
+      <c r="AE6" s="69"/>
+      <c r="AF6" s="69"/>
+      <c r="AG6" s="69"/>
+      <c r="AH6" s="69"/>
+      <c r="AI6" s="69"/>
+      <c r="AJ6" s="93"/>
       <c r="AK6" s="4"/>
       <c r="AL6" s="7"/>
       <c r="AM6" s="41" t="s">
@@ -2221,44 +2255,44 @@
       <c r="BT6" s="6"/>
     </row>
     <row r="7" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="76" t="s">
+      <c r="A7" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="77"/>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="88"/>
-      <c r="O7" s="88"/>
-      <c r="P7" s="88"/>
-      <c r="Q7" s="88"/>
-      <c r="R7" s="88"/>
-      <c r="S7" s="88"/>
-      <c r="T7" s="88"/>
-      <c r="U7" s="89"/>
-      <c r="V7" s="102"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="102"/>
+      <c r="Q7" s="102"/>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="102"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="75"/>
       <c r="W7" s="36"/>
       <c r="X7" s="36"/>
       <c r="Y7" s="36"/>
-      <c r="Z7" s="71"/>
-      <c r="AA7" s="73"/>
-      <c r="AB7" s="74"/>
-      <c r="AC7" s="74"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="75"/>
-      <c r="AF7" s="97"/>
-      <c r="AG7" s="74"/>
-      <c r="AH7" s="74"/>
-      <c r="AI7" s="74"/>
-      <c r="AJ7" s="107"/>
+      <c r="Z7" s="76"/>
+      <c r="AA7" s="65"/>
+      <c r="AB7" s="66"/>
+      <c r="AC7" s="66"/>
+      <c r="AD7" s="66"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="70"/>
+      <c r="AG7" s="66"/>
+      <c r="AH7" s="66"/>
+      <c r="AI7" s="66"/>
+      <c r="AJ7" s="82"/>
       <c r="AK7" s="4"/>
       <c r="AL7" s="7"/>
       <c r="AM7" s="42"/>
@@ -2297,45 +2331,47 @@
       <c r="BT7" s="6"/>
     </row>
     <row r="8" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="76"/>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="91"/>
-      <c r="J8" s="91"/>
-      <c r="K8" s="91"/>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="91"/>
-      <c r="O8" s="91"/>
-      <c r="P8" s="91"/>
-      <c r="Q8" s="91"/>
-      <c r="R8" s="91"/>
-      <c r="S8" s="91"/>
-      <c r="T8" s="91"/>
-      <c r="U8" s="92"/>
-      <c r="V8" s="102"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="104"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
+      <c r="H8" s="105"/>
+      <c r="I8" s="105"/>
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="105"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="105"/>
+      <c r="O8" s="105"/>
+      <c r="P8" s="105"/>
+      <c r="Q8" s="105"/>
+      <c r="R8" s="105"/>
+      <c r="S8" s="105"/>
+      <c r="T8" s="105"/>
+      <c r="U8" s="106"/>
+      <c r="V8" s="75"/>
       <c r="W8" s="36"/>
       <c r="X8" s="36"/>
       <c r="Y8" s="36"/>
-      <c r="Z8" s="71"/>
-      <c r="AA8" s="73"/>
-      <c r="AB8" s="74"/>
-      <c r="AC8" s="74"/>
-      <c r="AD8" s="74"/>
-      <c r="AE8" s="75"/>
-      <c r="AF8" s="97"/>
-      <c r="AG8" s="74"/>
-      <c r="AH8" s="74"/>
-      <c r="AI8" s="74"/>
-      <c r="AJ8" s="107"/>
+      <c r="Z8" s="76"/>
+      <c r="AA8" s="65"/>
+      <c r="AB8" s="66"/>
+      <c r="AC8" s="66"/>
+      <c r="AD8" s="66"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="70"/>
+      <c r="AG8" s="66"/>
+      <c r="AH8" s="66"/>
+      <c r="AI8" s="66"/>
+      <c r="AJ8" s="82"/>
       <c r="AK8" s="4"/>
       <c r="AL8" s="7"/>
-      <c r="AM8" s="41"/>
+      <c r="AM8" s="41" t="s">
+        <v>22</v>
+      </c>
       <c r="AN8" s="41"/>
       <c r="AO8" s="41"/>
       <c r="AP8" s="41"/>
@@ -2352,7 +2388,9 @@
       <c r="BA8" s="41"/>
       <c r="BB8" s="5"/>
       <c r="BC8" s="5"/>
-      <c r="BD8" s="41"/>
+      <c r="BD8" s="41" t="s">
+        <v>23</v>
+      </c>
       <c r="BE8" s="41"/>
       <c r="BF8" s="41"/>
       <c r="BG8" s="41"/>
@@ -2371,42 +2409,42 @@
       <c r="BT8" s="6"/>
     </row>
     <row r="9" spans="1:72" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="76"/>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="93"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="94"/>
-      <c r="J9" s="94"/>
-      <c r="K9" s="94"/>
-      <c r="L9" s="94"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="94"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
-      <c r="S9" s="94"/>
-      <c r="T9" s="94"/>
-      <c r="U9" s="95"/>
-      <c r="V9" s="99"/>
+      <c r="A9" s="81"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="108"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="108"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="108"/>
+      <c r="O9" s="108"/>
+      <c r="P9" s="108"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="108"/>
+      <c r="S9" s="108"/>
+      <c r="T9" s="108"/>
+      <c r="U9" s="109"/>
+      <c r="V9" s="72"/>
       <c r="W9" s="63"/>
       <c r="X9" s="63"/>
       <c r="Y9" s="63"/>
-      <c r="Z9" s="103"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="85"/>
-      <c r="AC9" s="85"/>
-      <c r="AD9" s="85"/>
-      <c r="AE9" s="86"/>
-      <c r="AF9" s="108"/>
-      <c r="AG9" s="85"/>
-      <c r="AH9" s="85"/>
-      <c r="AI9" s="85"/>
-      <c r="AJ9" s="109"/>
+      <c r="Z9" s="77"/>
+      <c r="AA9" s="99"/>
+      <c r="AB9" s="84"/>
+      <c r="AC9" s="84"/>
+      <c r="AD9" s="84"/>
+      <c r="AE9" s="100"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="84"/>
+      <c r="AH9" s="84"/>
+      <c r="AI9" s="84"/>
+      <c r="AJ9" s="85"/>
       <c r="AK9" s="4"/>
       <c r="AL9" s="7"/>
       <c r="AM9" s="36"/>
@@ -2445,44 +2483,44 @@
       <c r="BT9" s="6"/>
     </row>
     <row r="10" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="71" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="33"/>
       <c r="C10" s="33"/>
       <c r="D10" s="34"/>
-      <c r="E10" s="79"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="80"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="80"/>
-      <c r="M10" s="80"/>
-      <c r="N10" s="80"/>
-      <c r="O10" s="80"/>
-      <c r="P10" s="80"/>
-      <c r="Q10" s="80"/>
-      <c r="R10" s="80"/>
-      <c r="S10" s="80"/>
-      <c r="T10" s="80"/>
-      <c r="U10" s="80"/>
-      <c r="V10" s="80"/>
-      <c r="W10" s="80"/>
-      <c r="X10" s="80"/>
-      <c r="Y10" s="80"/>
-      <c r="Z10" s="80"/>
-      <c r="AA10" s="80"/>
-      <c r="AB10" s="80"/>
-      <c r="AC10" s="80"/>
-      <c r="AD10" s="80"/>
-      <c r="AE10" s="80"/>
-      <c r="AF10" s="80"/>
-      <c r="AG10" s="80"/>
-      <c r="AH10" s="80"/>
-      <c r="AI10" s="80"/>
-      <c r="AJ10" s="81"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="95"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="95"/>
+      <c r="J10" s="95"/>
+      <c r="K10" s="95"/>
+      <c r="L10" s="95"/>
+      <c r="M10" s="95"/>
+      <c r="N10" s="95"/>
+      <c r="O10" s="95"/>
+      <c r="P10" s="95"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="95"/>
+      <c r="S10" s="95"/>
+      <c r="T10" s="95"/>
+      <c r="U10" s="95"/>
+      <c r="V10" s="95"/>
+      <c r="W10" s="95"/>
+      <c r="X10" s="95"/>
+      <c r="Y10" s="95"/>
+      <c r="Z10" s="95"/>
+      <c r="AA10" s="95"/>
+      <c r="AB10" s="95"/>
+      <c r="AC10" s="95"/>
+      <c r="AD10" s="95"/>
+      <c r="AE10" s="95"/>
+      <c r="AF10" s="95"/>
+      <c r="AG10" s="95"/>
+      <c r="AH10" s="95"/>
+      <c r="AI10" s="95"/>
+      <c r="AJ10" s="96"/>
       <c r="AK10" s="4"/>
       <c r="AL10" s="7"/>
       <c r="AM10" s="32"/>
@@ -2521,11 +2559,11 @@
       <c r="BT10" s="6"/>
     </row>
     <row r="11" spans="1:72" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="99"/>
+      <c r="A11" s="72"/>
       <c r="B11" s="63"/>
       <c r="C11" s="63"/>
-      <c r="D11" s="100"/>
-      <c r="E11" s="82"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="97"/>
       <c r="F11" s="64"/>
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
@@ -2556,7 +2594,7 @@
       <c r="AG11" s="64"/>
       <c r="AH11" s="64"/>
       <c r="AI11" s="64"/>
-      <c r="AJ11" s="83"/>
+      <c r="AJ11" s="98"/>
       <c r="AK11" s="4"/>
       <c r="AL11" s="7"/>
       <c r="AM11" s="35"/>
@@ -3679,38 +3717,42 @@
       <c r="AJ26" s="6"/>
       <c r="AK26" s="4"/>
       <c r="AL26" s="7"/>
-      <c r="AM26" s="8"/>
-      <c r="AN26" s="5"/>
-      <c r="AO26" s="5"/>
-      <c r="AP26" s="5"/>
-      <c r="AQ26" s="5"/>
-      <c r="AR26" s="5"/>
-      <c r="AS26" s="5"/>
-      <c r="AT26" s="5"/>
-      <c r="AU26" s="5"/>
-      <c r="AV26" s="5"/>
-      <c r="AW26" s="5"/>
-      <c r="AX26" s="5"/>
-      <c r="AY26" s="5"/>
-      <c r="AZ26" s="5"/>
-      <c r="BA26" s="5"/>
+      <c r="AM26" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="AN26" s="41"/>
+      <c r="AO26" s="41"/>
+      <c r="AP26" s="41"/>
+      <c r="AQ26" s="41"/>
+      <c r="AR26" s="41"/>
+      <c r="AS26" s="41"/>
+      <c r="AT26" s="41"/>
+      <c r="AU26" s="41"/>
+      <c r="AV26" s="41"/>
+      <c r="AW26" s="41"/>
+      <c r="AX26" s="41"/>
+      <c r="AY26" s="41"/>
+      <c r="AZ26" s="41"/>
+      <c r="BA26" s="41"/>
       <c r="BB26" s="5"/>
       <c r="BC26" s="5"/>
-      <c r="BD26" s="5"/>
-      <c r="BE26" s="5"/>
-      <c r="BF26" s="5"/>
-      <c r="BG26" s="7"/>
-      <c r="BH26" s="5"/>
-      <c r="BI26" s="8"/>
-      <c r="BJ26" s="5"/>
-      <c r="BK26" s="5"/>
-      <c r="BL26" s="5"/>
-      <c r="BM26" s="5"/>
-      <c r="BN26" s="5"/>
-      <c r="BO26" s="5"/>
-      <c r="BP26" s="5"/>
-      <c r="BQ26" s="5"/>
-      <c r="BR26" s="5"/>
+      <c r="BD26" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="BE26" s="41"/>
+      <c r="BF26" s="41"/>
+      <c r="BG26" s="41"/>
+      <c r="BH26" s="41"/>
+      <c r="BI26" s="41"/>
+      <c r="BJ26" s="41"/>
+      <c r="BK26" s="41"/>
+      <c r="BL26" s="41"/>
+      <c r="BM26" s="41"/>
+      <c r="BN26" s="41"/>
+      <c r="BO26" s="41"/>
+      <c r="BP26" s="41"/>
+      <c r="BQ26" s="41"/>
+      <c r="BR26" s="41"/>
       <c r="BS26" s="5"/>
       <c r="BT26" s="6"/>
     </row>
@@ -3753,38 +3795,38 @@
       <c r="AJ27" s="6"/>
       <c r="AK27" s="4"/>
       <c r="AL27" s="7"/>
-      <c r="AM27" s="8"/>
-      <c r="AN27" s="5"/>
-      <c r="AO27" s="5"/>
-      <c r="AP27" s="5"/>
-      <c r="AQ27" s="5"/>
-      <c r="AR27" s="5"/>
-      <c r="AS27" s="5"/>
-      <c r="AT27" s="5"/>
-      <c r="AU27" s="5"/>
-      <c r="AV27" s="5"/>
-      <c r="AW27" s="5"/>
-      <c r="AX27" s="5"/>
-      <c r="AY27" s="5"/>
-      <c r="AZ27" s="5"/>
-      <c r="BA27" s="5"/>
+      <c r="AM27" s="36"/>
+      <c r="AN27" s="36"/>
+      <c r="AO27" s="36"/>
+      <c r="AP27" s="36"/>
+      <c r="AQ27" s="36"/>
+      <c r="AR27" s="36"/>
+      <c r="AS27" s="36"/>
+      <c r="AT27" s="36"/>
+      <c r="AU27" s="36"/>
+      <c r="AV27" s="36"/>
+      <c r="AW27" s="36"/>
+      <c r="AX27" s="36"/>
+      <c r="AY27" s="36"/>
+      <c r="AZ27" s="36"/>
+      <c r="BA27" s="36"/>
       <c r="BB27" s="5"/>
       <c r="BC27" s="5"/>
-      <c r="BD27" s="5"/>
-      <c r="BE27" s="5"/>
-      <c r="BF27" s="5"/>
-      <c r="BG27" s="7"/>
-      <c r="BH27" s="5"/>
-      <c r="BI27" s="8"/>
-      <c r="BJ27" s="5"/>
-      <c r="BK27" s="5"/>
-      <c r="BL27" s="5"/>
-      <c r="BM27" s="5"/>
-      <c r="BN27" s="5"/>
-      <c r="BO27" s="5"/>
-      <c r="BP27" s="5"/>
-      <c r="BQ27" s="5"/>
-      <c r="BR27" s="5"/>
+      <c r="BD27" s="36"/>
+      <c r="BE27" s="36"/>
+      <c r="BF27" s="36"/>
+      <c r="BG27" s="36"/>
+      <c r="BH27" s="36"/>
+      <c r="BI27" s="36"/>
+      <c r="BJ27" s="36"/>
+      <c r="BK27" s="36"/>
+      <c r="BL27" s="36"/>
+      <c r="BM27" s="36"/>
+      <c r="BN27" s="36"/>
+      <c r="BO27" s="36"/>
+      <c r="BP27" s="36"/>
+      <c r="BQ27" s="36"/>
+      <c r="BR27" s="36"/>
       <c r="BS27" s="5"/>
       <c r="BT27" s="6"/>
     </row>
@@ -3827,38 +3869,38 @@
       <c r="AJ28" s="6"/>
       <c r="AK28" s="4"/>
       <c r="AL28" s="7"/>
-      <c r="AM28" s="8"/>
-      <c r="AN28" s="5"/>
-      <c r="AO28" s="5"/>
-      <c r="AP28" s="5"/>
-      <c r="AQ28" s="5"/>
-      <c r="AR28" s="5"/>
-      <c r="AS28" s="5"/>
-      <c r="AT28" s="5"/>
-      <c r="AU28" s="5"/>
-      <c r="AV28" s="5"/>
-      <c r="AW28" s="5"/>
-      <c r="AX28" s="5"/>
-      <c r="AY28" s="5"/>
-      <c r="AZ28" s="5"/>
-      <c r="BA28" s="5"/>
+      <c r="AM28" s="32"/>
+      <c r="AN28" s="33"/>
+      <c r="AO28" s="33"/>
+      <c r="AP28" s="33"/>
+      <c r="AQ28" s="33"/>
+      <c r="AR28" s="33"/>
+      <c r="AS28" s="33"/>
+      <c r="AT28" s="33"/>
+      <c r="AU28" s="33"/>
+      <c r="AV28" s="33"/>
+      <c r="AW28" s="33"/>
+      <c r="AX28" s="33"/>
+      <c r="AY28" s="33"/>
+      <c r="AZ28" s="33"/>
+      <c r="BA28" s="34"/>
       <c r="BB28" s="5"/>
       <c r="BC28" s="5"/>
-      <c r="BD28" s="5"/>
-      <c r="BE28" s="5"/>
-      <c r="BF28" s="5"/>
-      <c r="BG28" s="7"/>
-      <c r="BH28" s="5"/>
-      <c r="BI28" s="8"/>
-      <c r="BJ28" s="5"/>
-      <c r="BK28" s="5"/>
-      <c r="BL28" s="5"/>
-      <c r="BM28" s="5"/>
-      <c r="BN28" s="5"/>
-      <c r="BO28" s="5"/>
-      <c r="BP28" s="5"/>
-      <c r="BQ28" s="5"/>
-      <c r="BR28" s="5"/>
+      <c r="BD28" s="32"/>
+      <c r="BE28" s="33"/>
+      <c r="BF28" s="33"/>
+      <c r="BG28" s="33"/>
+      <c r="BH28" s="33"/>
+      <c r="BI28" s="33"/>
+      <c r="BJ28" s="33"/>
+      <c r="BK28" s="33"/>
+      <c r="BL28" s="33"/>
+      <c r="BM28" s="33"/>
+      <c r="BN28" s="33"/>
+      <c r="BO28" s="33"/>
+      <c r="BP28" s="33"/>
+      <c r="BQ28" s="33"/>
+      <c r="BR28" s="34"/>
       <c r="BS28" s="5"/>
       <c r="BT28" s="6"/>
     </row>
@@ -3905,38 +3947,38 @@
       <c r="AJ29" s="6"/>
       <c r="AK29" s="4"/>
       <c r="AL29" s="7"/>
-      <c r="AM29" s="8"/>
-      <c r="AN29" s="5"/>
-      <c r="AO29" s="5"/>
-      <c r="AP29" s="5"/>
-      <c r="AQ29" s="5"/>
-      <c r="AR29" s="5"/>
-      <c r="AS29" s="5"/>
-      <c r="AT29" s="5"/>
-      <c r="AU29" s="5"/>
-      <c r="AV29" s="5"/>
-      <c r="AW29" s="5"/>
-      <c r="AX29" s="5"/>
-      <c r="AY29" s="5"/>
-      <c r="AZ29" s="5"/>
-      <c r="BA29" s="5"/>
+      <c r="AM29" s="35"/>
+      <c r="AN29" s="36"/>
+      <c r="AO29" s="36"/>
+      <c r="AP29" s="36"/>
+      <c r="AQ29" s="36"/>
+      <c r="AR29" s="36"/>
+      <c r="AS29" s="36"/>
+      <c r="AT29" s="36"/>
+      <c r="AU29" s="36"/>
+      <c r="AV29" s="36"/>
+      <c r="AW29" s="36"/>
+      <c r="AX29" s="36"/>
+      <c r="AY29" s="36"/>
+      <c r="AZ29" s="36"/>
+      <c r="BA29" s="37"/>
       <c r="BB29" s="5"/>
       <c r="BC29" s="5"/>
-      <c r="BD29" s="5"/>
-      <c r="BE29" s="5"/>
-      <c r="BF29" s="5"/>
-      <c r="BG29" s="7"/>
-      <c r="BH29" s="5"/>
-      <c r="BI29" s="8"/>
-      <c r="BJ29" s="5"/>
-      <c r="BK29" s="5"/>
-      <c r="BL29" s="5"/>
-      <c r="BM29" s="5"/>
-      <c r="BN29" s="5"/>
-      <c r="BO29" s="5"/>
-      <c r="BP29" s="5"/>
-      <c r="BQ29" s="5"/>
-      <c r="BR29" s="5"/>
+      <c r="BD29" s="35"/>
+      <c r="BE29" s="36"/>
+      <c r="BF29" s="36"/>
+      <c r="BG29" s="36"/>
+      <c r="BH29" s="36"/>
+      <c r="BI29" s="36"/>
+      <c r="BJ29" s="36"/>
+      <c r="BK29" s="36"/>
+      <c r="BL29" s="36"/>
+      <c r="BM29" s="36"/>
+      <c r="BN29" s="36"/>
+      <c r="BO29" s="36"/>
+      <c r="BP29" s="36"/>
+      <c r="BQ29" s="36"/>
+      <c r="BR29" s="37"/>
       <c r="BS29" s="5"/>
       <c r="BT29" s="6"/>
     </row>
@@ -3979,38 +4021,38 @@
       <c r="AJ30" s="6"/>
       <c r="AK30" s="4"/>
       <c r="AL30" s="7"/>
-      <c r="AM30" s="8"/>
-      <c r="AN30" s="5"/>
-      <c r="AO30" s="5"/>
-      <c r="AP30" s="5"/>
-      <c r="AQ30" s="5"/>
-      <c r="AR30" s="5"/>
-      <c r="AS30" s="5"/>
-      <c r="AT30" s="5"/>
-      <c r="AU30" s="5"/>
-      <c r="AV30" s="5"/>
-      <c r="AW30" s="5"/>
-      <c r="AX30" s="5"/>
-      <c r="AY30" s="5"/>
-      <c r="AZ30" s="5"/>
-      <c r="BA30" s="5"/>
+      <c r="AM30" s="35"/>
+      <c r="AN30" s="36"/>
+      <c r="AO30" s="36"/>
+      <c r="AP30" s="36"/>
+      <c r="AQ30" s="36"/>
+      <c r="AR30" s="36"/>
+      <c r="AS30" s="36"/>
+      <c r="AT30" s="36"/>
+      <c r="AU30" s="36"/>
+      <c r="AV30" s="36"/>
+      <c r="AW30" s="36"/>
+      <c r="AX30" s="36"/>
+      <c r="AY30" s="36"/>
+      <c r="AZ30" s="36"/>
+      <c r="BA30" s="37"/>
       <c r="BB30" s="5"/>
       <c r="BC30" s="5"/>
-      <c r="BD30" s="5"/>
-      <c r="BE30" s="5"/>
-      <c r="BF30" s="5"/>
-      <c r="BG30" s="7"/>
-      <c r="BH30" s="5"/>
-      <c r="BI30" s="8"/>
-      <c r="BJ30" s="5"/>
-      <c r="BK30" s="5"/>
-      <c r="BL30" s="5"/>
-      <c r="BM30" s="5"/>
-      <c r="BN30" s="5"/>
-      <c r="BO30" s="5"/>
-      <c r="BP30" s="5"/>
-      <c r="BQ30" s="5"/>
-      <c r="BR30" s="5"/>
+      <c r="BD30" s="35"/>
+      <c r="BE30" s="36"/>
+      <c r="BF30" s="36"/>
+      <c r="BG30" s="36"/>
+      <c r="BH30" s="36"/>
+      <c r="BI30" s="36"/>
+      <c r="BJ30" s="36"/>
+      <c r="BK30" s="36"/>
+      <c r="BL30" s="36"/>
+      <c r="BM30" s="36"/>
+      <c r="BN30" s="36"/>
+      <c r="BO30" s="36"/>
+      <c r="BP30" s="36"/>
+      <c r="BQ30" s="36"/>
+      <c r="BR30" s="37"/>
       <c r="BS30" s="5"/>
       <c r="BT30" s="6"/>
     </row>
@@ -4053,38 +4095,38 @@
       <c r="AJ31" s="6"/>
       <c r="AK31" s="4"/>
       <c r="AL31" s="7"/>
-      <c r="AM31" s="8"/>
-      <c r="AN31" s="5"/>
-      <c r="AO31" s="5"/>
-      <c r="AP31" s="5"/>
-      <c r="AQ31" s="5"/>
-      <c r="AR31" s="5"/>
-      <c r="AS31" s="5"/>
-      <c r="AT31" s="5"/>
-      <c r="AU31" s="5"/>
-      <c r="AV31" s="5"/>
-      <c r="AW31" s="5"/>
-      <c r="AX31" s="5"/>
-      <c r="AY31" s="5"/>
-      <c r="AZ31" s="5"/>
-      <c r="BA31" s="5"/>
+      <c r="AM31" s="35"/>
+      <c r="AN31" s="36"/>
+      <c r="AO31" s="36"/>
+      <c r="AP31" s="36"/>
+      <c r="AQ31" s="36"/>
+      <c r="AR31" s="36"/>
+      <c r="AS31" s="36"/>
+      <c r="AT31" s="36"/>
+      <c r="AU31" s="36"/>
+      <c r="AV31" s="36"/>
+      <c r="AW31" s="36"/>
+      <c r="AX31" s="36"/>
+      <c r="AY31" s="36"/>
+      <c r="AZ31" s="36"/>
+      <c r="BA31" s="37"/>
       <c r="BB31" s="5"/>
       <c r="BC31" s="5"/>
-      <c r="BD31" s="5"/>
-      <c r="BE31" s="5"/>
-      <c r="BF31" s="5"/>
-      <c r="BG31" s="7"/>
-      <c r="BH31" s="5"/>
-      <c r="BI31" s="8"/>
-      <c r="BJ31" s="5"/>
-      <c r="BK31" s="5"/>
-      <c r="BL31" s="5"/>
-      <c r="BM31" s="5"/>
-      <c r="BN31" s="5"/>
-      <c r="BO31" s="5"/>
-      <c r="BP31" s="5"/>
-      <c r="BQ31" s="5"/>
-      <c r="BR31" s="5"/>
+      <c r="BD31" s="35"/>
+      <c r="BE31" s="36"/>
+      <c r="BF31" s="36"/>
+      <c r="BG31" s="36"/>
+      <c r="BH31" s="36"/>
+      <c r="BI31" s="36"/>
+      <c r="BJ31" s="36"/>
+      <c r="BK31" s="36"/>
+      <c r="BL31" s="36"/>
+      <c r="BM31" s="36"/>
+      <c r="BN31" s="36"/>
+      <c r="BO31" s="36"/>
+      <c r="BP31" s="36"/>
+      <c r="BQ31" s="36"/>
+      <c r="BR31" s="37"/>
       <c r="BS31" s="5"/>
       <c r="BT31" s="6"/>
     </row>
@@ -4127,38 +4169,38 @@
       <c r="AJ32" s="6"/>
       <c r="AK32" s="4"/>
       <c r="AL32" s="7"/>
-      <c r="AM32" s="8"/>
-      <c r="AN32" s="5"/>
-      <c r="AO32" s="5"/>
-      <c r="AP32" s="5"/>
-      <c r="AQ32" s="5"/>
-      <c r="AR32" s="5"/>
-      <c r="AS32" s="5"/>
-      <c r="AT32" s="5"/>
-      <c r="AU32" s="5"/>
-      <c r="AV32" s="5"/>
-      <c r="AW32" s="5"/>
-      <c r="AX32" s="5"/>
-      <c r="AY32" s="5"/>
-      <c r="AZ32" s="5"/>
-      <c r="BA32" s="5"/>
+      <c r="AM32" s="35"/>
+      <c r="AN32" s="36"/>
+      <c r="AO32" s="36"/>
+      <c r="AP32" s="36"/>
+      <c r="AQ32" s="36"/>
+      <c r="AR32" s="36"/>
+      <c r="AS32" s="36"/>
+      <c r="AT32" s="36"/>
+      <c r="AU32" s="36"/>
+      <c r="AV32" s="36"/>
+      <c r="AW32" s="36"/>
+      <c r="AX32" s="36"/>
+      <c r="AY32" s="36"/>
+      <c r="AZ32" s="36"/>
+      <c r="BA32" s="37"/>
       <c r="BB32" s="5"/>
       <c r="BC32" s="5"/>
-      <c r="BD32" s="5"/>
-      <c r="BE32" s="5"/>
-      <c r="BF32" s="5"/>
-      <c r="BG32" s="7"/>
-      <c r="BH32" s="5"/>
-      <c r="BI32" s="8"/>
-      <c r="BJ32" s="5"/>
-      <c r="BK32" s="5"/>
-      <c r="BL32" s="5"/>
-      <c r="BM32" s="5"/>
-      <c r="BN32" s="5"/>
-      <c r="BO32" s="5"/>
-      <c r="BP32" s="5"/>
-      <c r="BQ32" s="5"/>
-      <c r="BR32" s="5"/>
+      <c r="BD32" s="35"/>
+      <c r="BE32" s="36"/>
+      <c r="BF32" s="36"/>
+      <c r="BG32" s="36"/>
+      <c r="BH32" s="36"/>
+      <c r="BI32" s="36"/>
+      <c r="BJ32" s="36"/>
+      <c r="BK32" s="36"/>
+      <c r="BL32" s="36"/>
+      <c r="BM32" s="36"/>
+      <c r="BN32" s="36"/>
+      <c r="BO32" s="36"/>
+      <c r="BP32" s="36"/>
+      <c r="BQ32" s="36"/>
+      <c r="BR32" s="37"/>
       <c r="BS32" s="5"/>
       <c r="BT32" s="6"/>
     </row>
@@ -4201,38 +4243,38 @@
       <c r="AJ33" s="6"/>
       <c r="AK33" s="4"/>
       <c r="AL33" s="7"/>
-      <c r="AM33" s="8"/>
-      <c r="AN33" s="5"/>
-      <c r="AO33" s="5"/>
-      <c r="AP33" s="5"/>
-      <c r="AQ33" s="5"/>
-      <c r="AR33" s="5"/>
-      <c r="AS33" s="5"/>
-      <c r="AT33" s="5"/>
-      <c r="AU33" s="5"/>
-      <c r="AV33" s="5"/>
-      <c r="AW33" s="5"/>
-      <c r="AX33" s="5"/>
-      <c r="AY33" s="5"/>
-      <c r="AZ33" s="5"/>
-      <c r="BA33" s="5"/>
+      <c r="AM33" s="35"/>
+      <c r="AN33" s="36"/>
+      <c r="AO33" s="36"/>
+      <c r="AP33" s="36"/>
+      <c r="AQ33" s="36"/>
+      <c r="AR33" s="36"/>
+      <c r="AS33" s="36"/>
+      <c r="AT33" s="36"/>
+      <c r="AU33" s="36"/>
+      <c r="AV33" s="36"/>
+      <c r="AW33" s="36"/>
+      <c r="AX33" s="36"/>
+      <c r="AY33" s="36"/>
+      <c r="AZ33" s="36"/>
+      <c r="BA33" s="37"/>
       <c r="BB33" s="5"/>
       <c r="BC33" s="5"/>
-      <c r="BD33" s="5"/>
-      <c r="BE33" s="5"/>
-      <c r="BF33" s="5"/>
-      <c r="BG33" s="7"/>
-      <c r="BH33" s="5"/>
-      <c r="BI33" s="8"/>
-      <c r="BJ33" s="5"/>
-      <c r="BK33" s="5"/>
-      <c r="BL33" s="5"/>
-      <c r="BM33" s="5"/>
-      <c r="BN33" s="5"/>
-      <c r="BO33" s="5"/>
-      <c r="BP33" s="5"/>
-      <c r="BQ33" s="5"/>
-      <c r="BR33" s="5"/>
+      <c r="BD33" s="35"/>
+      <c r="BE33" s="36"/>
+      <c r="BF33" s="36"/>
+      <c r="BG33" s="36"/>
+      <c r="BH33" s="36"/>
+      <c r="BI33" s="36"/>
+      <c r="BJ33" s="36"/>
+      <c r="BK33" s="36"/>
+      <c r="BL33" s="36"/>
+      <c r="BM33" s="36"/>
+      <c r="BN33" s="36"/>
+      <c r="BO33" s="36"/>
+      <c r="BP33" s="36"/>
+      <c r="BQ33" s="36"/>
+      <c r="BR33" s="37"/>
       <c r="BS33" s="5"/>
       <c r="BT33" s="6"/>
     </row>
@@ -4275,38 +4317,38 @@
       <c r="AJ34" s="6"/>
       <c r="AK34" s="4"/>
       <c r="AL34" s="7"/>
-      <c r="AM34" s="8"/>
-      <c r="AN34" s="5"/>
-      <c r="AO34" s="5"/>
-      <c r="AP34" s="5"/>
-      <c r="AQ34" s="5"/>
-      <c r="AR34" s="5"/>
-      <c r="AS34" s="5"/>
-      <c r="AT34" s="5"/>
-      <c r="AU34" s="5"/>
-      <c r="AV34" s="5"/>
-      <c r="AW34" s="5"/>
-      <c r="AX34" s="5"/>
-      <c r="AY34" s="5"/>
-      <c r="AZ34" s="5"/>
-      <c r="BA34" s="5"/>
+      <c r="AM34" s="35"/>
+      <c r="AN34" s="36"/>
+      <c r="AO34" s="36"/>
+      <c r="AP34" s="36"/>
+      <c r="AQ34" s="36"/>
+      <c r="AR34" s="36"/>
+      <c r="AS34" s="36"/>
+      <c r="AT34" s="36"/>
+      <c r="AU34" s="36"/>
+      <c r="AV34" s="36"/>
+      <c r="AW34" s="36"/>
+      <c r="AX34" s="36"/>
+      <c r="AY34" s="36"/>
+      <c r="AZ34" s="36"/>
+      <c r="BA34" s="37"/>
       <c r="BB34" s="5"/>
       <c r="BC34" s="5"/>
-      <c r="BD34" s="5"/>
-      <c r="BE34" s="5"/>
-      <c r="BF34" s="5"/>
-      <c r="BG34" s="7"/>
-      <c r="BH34" s="5"/>
-      <c r="BI34" s="8"/>
-      <c r="BJ34" s="5"/>
-      <c r="BK34" s="5"/>
-      <c r="BL34" s="5"/>
-      <c r="BM34" s="5"/>
-      <c r="BN34" s="5"/>
-      <c r="BO34" s="5"/>
-      <c r="BP34" s="5"/>
-      <c r="BQ34" s="5"/>
-      <c r="BR34" s="5"/>
+      <c r="BD34" s="35"/>
+      <c r="BE34" s="36"/>
+      <c r="BF34" s="36"/>
+      <c r="BG34" s="36"/>
+      <c r="BH34" s="36"/>
+      <c r="BI34" s="36"/>
+      <c r="BJ34" s="36"/>
+      <c r="BK34" s="36"/>
+      <c r="BL34" s="36"/>
+      <c r="BM34" s="36"/>
+      <c r="BN34" s="36"/>
+      <c r="BO34" s="36"/>
+      <c r="BP34" s="36"/>
+      <c r="BQ34" s="36"/>
+      <c r="BR34" s="37"/>
       <c r="BS34" s="5"/>
       <c r="BT34" s="6"/>
     </row>
@@ -4349,38 +4391,38 @@
       <c r="AJ35" s="6"/>
       <c r="AK35" s="4"/>
       <c r="AL35" s="7"/>
-      <c r="AM35" s="8"/>
-      <c r="AN35" s="5"/>
-      <c r="AO35" s="5"/>
-      <c r="AP35" s="5"/>
-      <c r="AQ35" s="5"/>
-      <c r="AR35" s="5"/>
-      <c r="AS35" s="5"/>
-      <c r="AT35" s="5"/>
-      <c r="AU35" s="5"/>
-      <c r="AV35" s="5"/>
-      <c r="AW35" s="5"/>
-      <c r="AX35" s="5"/>
-      <c r="AY35" s="5"/>
-      <c r="AZ35" s="5"/>
-      <c r="BA35" s="5"/>
+      <c r="AM35" s="35"/>
+      <c r="AN35" s="36"/>
+      <c r="AO35" s="36"/>
+      <c r="AP35" s="36"/>
+      <c r="AQ35" s="36"/>
+      <c r="AR35" s="36"/>
+      <c r="AS35" s="36"/>
+      <c r="AT35" s="36"/>
+      <c r="AU35" s="36"/>
+      <c r="AV35" s="36"/>
+      <c r="AW35" s="36"/>
+      <c r="AX35" s="36"/>
+      <c r="AY35" s="36"/>
+      <c r="AZ35" s="36"/>
+      <c r="BA35" s="37"/>
       <c r="BB35" s="5"/>
       <c r="BC35" s="5"/>
-      <c r="BD35" s="5"/>
-      <c r="BE35" s="5"/>
-      <c r="BF35" s="5"/>
-      <c r="BG35" s="7"/>
-      <c r="BH35" s="5"/>
-      <c r="BI35" s="8"/>
-      <c r="BJ35" s="5"/>
-      <c r="BK35" s="5"/>
-      <c r="BL35" s="5"/>
-      <c r="BM35" s="5"/>
-      <c r="BN35" s="5"/>
-      <c r="BO35" s="5"/>
-      <c r="BP35" s="5"/>
-      <c r="BQ35" s="5"/>
-      <c r="BR35" s="5"/>
+      <c r="BD35" s="35"/>
+      <c r="BE35" s="36"/>
+      <c r="BF35" s="36"/>
+      <c r="BG35" s="36"/>
+      <c r="BH35" s="36"/>
+      <c r="BI35" s="36"/>
+      <c r="BJ35" s="36"/>
+      <c r="BK35" s="36"/>
+      <c r="BL35" s="36"/>
+      <c r="BM35" s="36"/>
+      <c r="BN35" s="36"/>
+      <c r="BO35" s="36"/>
+      <c r="BP35" s="36"/>
+      <c r="BQ35" s="36"/>
+      <c r="BR35" s="37"/>
       <c r="BS35" s="5"/>
       <c r="BT35" s="6"/>
     </row>
@@ -4427,38 +4469,38 @@
       <c r="AJ36" s="6"/>
       <c r="AK36" s="4"/>
       <c r="AL36" s="7"/>
-      <c r="AM36" s="8"/>
-      <c r="AN36" s="5"/>
-      <c r="AO36" s="5"/>
-      <c r="AP36" s="5"/>
-      <c r="AQ36" s="5"/>
-      <c r="AR36" s="5"/>
-      <c r="AS36" s="5"/>
-      <c r="AT36" s="5"/>
-      <c r="AU36" s="5"/>
-      <c r="AV36" s="5"/>
-      <c r="AW36" s="5"/>
-      <c r="AX36" s="5"/>
-      <c r="AY36" s="5"/>
-      <c r="AZ36" s="5"/>
-      <c r="BA36" s="5"/>
+      <c r="AM36" s="35"/>
+      <c r="AN36" s="36"/>
+      <c r="AO36" s="36"/>
+      <c r="AP36" s="36"/>
+      <c r="AQ36" s="36"/>
+      <c r="AR36" s="36"/>
+      <c r="AS36" s="36"/>
+      <c r="AT36" s="36"/>
+      <c r="AU36" s="36"/>
+      <c r="AV36" s="36"/>
+      <c r="AW36" s="36"/>
+      <c r="AX36" s="36"/>
+      <c r="AY36" s="36"/>
+      <c r="AZ36" s="36"/>
+      <c r="BA36" s="37"/>
       <c r="BB36" s="5"/>
       <c r="BC36" s="5"/>
-      <c r="BD36" s="5"/>
-      <c r="BE36" s="5"/>
-      <c r="BF36" s="5"/>
-      <c r="BG36" s="7"/>
-      <c r="BH36" s="5"/>
-      <c r="BI36" s="8"/>
-      <c r="BJ36" s="5"/>
-      <c r="BK36" s="5"/>
-      <c r="BL36" s="5"/>
-      <c r="BM36" s="5"/>
-      <c r="BN36" s="5"/>
-      <c r="BO36" s="5"/>
-      <c r="BP36" s="5"/>
-      <c r="BQ36" s="5"/>
-      <c r="BR36" s="5"/>
+      <c r="BD36" s="35"/>
+      <c r="BE36" s="36"/>
+      <c r="BF36" s="36"/>
+      <c r="BG36" s="36"/>
+      <c r="BH36" s="36"/>
+      <c r="BI36" s="36"/>
+      <c r="BJ36" s="36"/>
+      <c r="BK36" s="36"/>
+      <c r="BL36" s="36"/>
+      <c r="BM36" s="36"/>
+      <c r="BN36" s="36"/>
+      <c r="BO36" s="36"/>
+      <c r="BP36" s="36"/>
+      <c r="BQ36" s="36"/>
+      <c r="BR36" s="37"/>
       <c r="BS36" s="5"/>
       <c r="BT36" s="6"/>
     </row>
@@ -4501,38 +4543,38 @@
       <c r="AJ37" s="6"/>
       <c r="AK37" s="4"/>
       <c r="AL37" s="7"/>
-      <c r="AM37" s="8"/>
-      <c r="AN37" s="5"/>
-      <c r="AO37" s="5"/>
-      <c r="AP37" s="5"/>
-      <c r="AQ37" s="5"/>
-      <c r="AR37" s="5"/>
-      <c r="AS37" s="5"/>
-      <c r="AT37" s="5"/>
-      <c r="AU37" s="5"/>
-      <c r="AV37" s="5"/>
-      <c r="AW37" s="5"/>
-      <c r="AX37" s="5"/>
-      <c r="AY37" s="5"/>
-      <c r="AZ37" s="5"/>
-      <c r="BA37" s="5"/>
+      <c r="AM37" s="35"/>
+      <c r="AN37" s="36"/>
+      <c r="AO37" s="36"/>
+      <c r="AP37" s="36"/>
+      <c r="AQ37" s="36"/>
+      <c r="AR37" s="36"/>
+      <c r="AS37" s="36"/>
+      <c r="AT37" s="36"/>
+      <c r="AU37" s="36"/>
+      <c r="AV37" s="36"/>
+      <c r="AW37" s="36"/>
+      <c r="AX37" s="36"/>
+      <c r="AY37" s="36"/>
+      <c r="AZ37" s="36"/>
+      <c r="BA37" s="37"/>
       <c r="BB37" s="5"/>
       <c r="BC37" s="5"/>
-      <c r="BD37" s="5"/>
-      <c r="BE37" s="5"/>
-      <c r="BF37" s="5"/>
-      <c r="BG37" s="7"/>
-      <c r="BH37" s="5"/>
-      <c r="BI37" s="8"/>
-      <c r="BJ37" s="5"/>
-      <c r="BK37" s="5"/>
-      <c r="BL37" s="5"/>
-      <c r="BM37" s="5"/>
-      <c r="BN37" s="5"/>
-      <c r="BO37" s="5"/>
-      <c r="BP37" s="5"/>
-      <c r="BQ37" s="5"/>
-      <c r="BR37" s="5"/>
+      <c r="BD37" s="35"/>
+      <c r="BE37" s="36"/>
+      <c r="BF37" s="36"/>
+      <c r="BG37" s="36"/>
+      <c r="BH37" s="36"/>
+      <c r="BI37" s="36"/>
+      <c r="BJ37" s="36"/>
+      <c r="BK37" s="36"/>
+      <c r="BL37" s="36"/>
+      <c r="BM37" s="36"/>
+      <c r="BN37" s="36"/>
+      <c r="BO37" s="36"/>
+      <c r="BP37" s="36"/>
+      <c r="BQ37" s="36"/>
+      <c r="BR37" s="37"/>
       <c r="BS37" s="5"/>
       <c r="BT37" s="6"/>
     </row>
@@ -4575,38 +4617,38 @@
       <c r="AJ38" s="6"/>
       <c r="AK38" s="4"/>
       <c r="AL38" s="7"/>
-      <c r="AM38" s="8"/>
-      <c r="AN38" s="5"/>
-      <c r="AO38" s="5"/>
-      <c r="AP38" s="5"/>
-      <c r="AQ38" s="5"/>
-      <c r="AR38" s="5"/>
-      <c r="AS38" s="5"/>
-      <c r="AT38" s="5"/>
-      <c r="AU38" s="5"/>
-      <c r="AV38" s="5"/>
-      <c r="AW38" s="5"/>
-      <c r="AX38" s="5"/>
-      <c r="AY38" s="5"/>
-      <c r="AZ38" s="5"/>
-      <c r="BA38" s="5"/>
+      <c r="AM38" s="35"/>
+      <c r="AN38" s="36"/>
+      <c r="AO38" s="36"/>
+      <c r="AP38" s="36"/>
+      <c r="AQ38" s="36"/>
+      <c r="AR38" s="36"/>
+      <c r="AS38" s="36"/>
+      <c r="AT38" s="36"/>
+      <c r="AU38" s="36"/>
+      <c r="AV38" s="36"/>
+      <c r="AW38" s="36"/>
+      <c r="AX38" s="36"/>
+      <c r="AY38" s="36"/>
+      <c r="AZ38" s="36"/>
+      <c r="BA38" s="37"/>
       <c r="BB38" s="5"/>
       <c r="BC38" s="5"/>
-      <c r="BD38" s="5"/>
-      <c r="BE38" s="5"/>
-      <c r="BF38" s="5"/>
-      <c r="BG38" s="7"/>
-      <c r="BH38" s="5"/>
-      <c r="BI38" s="8"/>
-      <c r="BJ38" s="5"/>
-      <c r="BK38" s="5"/>
-      <c r="BL38" s="5"/>
-      <c r="BM38" s="5"/>
-      <c r="BN38" s="5"/>
-      <c r="BO38" s="5"/>
-      <c r="BP38" s="5"/>
-      <c r="BQ38" s="5"/>
-      <c r="BR38" s="5"/>
+      <c r="BD38" s="35"/>
+      <c r="BE38" s="36"/>
+      <c r="BF38" s="36"/>
+      <c r="BG38" s="36"/>
+      <c r="BH38" s="36"/>
+      <c r="BI38" s="36"/>
+      <c r="BJ38" s="36"/>
+      <c r="BK38" s="36"/>
+      <c r="BL38" s="36"/>
+      <c r="BM38" s="36"/>
+      <c r="BN38" s="36"/>
+      <c r="BO38" s="36"/>
+      <c r="BP38" s="36"/>
+      <c r="BQ38" s="36"/>
+      <c r="BR38" s="37"/>
       <c r="BS38" s="5"/>
       <c r="BT38" s="6"/>
     </row>
@@ -4649,38 +4691,38 @@
       <c r="AJ39" s="6"/>
       <c r="AK39" s="4"/>
       <c r="AL39" s="7"/>
-      <c r="AM39" s="8"/>
-      <c r="AN39" s="5"/>
-      <c r="AO39" s="5"/>
-      <c r="AP39" s="5"/>
-      <c r="AQ39" s="5"/>
-      <c r="AR39" s="5"/>
-      <c r="AS39" s="5"/>
-      <c r="AT39" s="5"/>
-      <c r="AU39" s="5"/>
-      <c r="AV39" s="5"/>
-      <c r="AW39" s="5"/>
-      <c r="AX39" s="5"/>
-      <c r="AY39" s="5"/>
-      <c r="AZ39" s="5"/>
-      <c r="BA39" s="5"/>
+      <c r="AM39" s="35"/>
+      <c r="AN39" s="36"/>
+      <c r="AO39" s="36"/>
+      <c r="AP39" s="36"/>
+      <c r="AQ39" s="36"/>
+      <c r="AR39" s="36"/>
+      <c r="AS39" s="36"/>
+      <c r="AT39" s="36"/>
+      <c r="AU39" s="36"/>
+      <c r="AV39" s="36"/>
+      <c r="AW39" s="36"/>
+      <c r="AX39" s="36"/>
+      <c r="AY39" s="36"/>
+      <c r="AZ39" s="36"/>
+      <c r="BA39" s="37"/>
       <c r="BB39" s="5"/>
       <c r="BC39" s="5"/>
-      <c r="BD39" s="5"/>
-      <c r="BE39" s="5"/>
-      <c r="BF39" s="5"/>
-      <c r="BG39" s="7"/>
-      <c r="BH39" s="5"/>
-      <c r="BI39" s="8"/>
-      <c r="BJ39" s="5"/>
-      <c r="BK39" s="5"/>
-      <c r="BL39" s="5"/>
-      <c r="BM39" s="5"/>
-      <c r="BN39" s="5"/>
-      <c r="BO39" s="5"/>
-      <c r="BP39" s="5"/>
-      <c r="BQ39" s="5"/>
-      <c r="BR39" s="5"/>
+      <c r="BD39" s="35"/>
+      <c r="BE39" s="36"/>
+      <c r="BF39" s="36"/>
+      <c r="BG39" s="36"/>
+      <c r="BH39" s="36"/>
+      <c r="BI39" s="36"/>
+      <c r="BJ39" s="36"/>
+      <c r="BK39" s="36"/>
+      <c r="BL39" s="36"/>
+      <c r="BM39" s="36"/>
+      <c r="BN39" s="36"/>
+      <c r="BO39" s="36"/>
+      <c r="BP39" s="36"/>
+      <c r="BQ39" s="36"/>
+      <c r="BR39" s="37"/>
       <c r="BS39" s="5"/>
       <c r="BT39" s="6"/>
     </row>
@@ -4723,38 +4765,38 @@
       <c r="AJ40" s="6"/>
       <c r="AK40" s="4"/>
       <c r="AL40" s="7"/>
-      <c r="AM40" s="8"/>
-      <c r="AN40" s="5"/>
-      <c r="AO40" s="5"/>
-      <c r="AP40" s="5"/>
-      <c r="AQ40" s="5"/>
-      <c r="AR40" s="5"/>
-      <c r="AS40" s="5"/>
-      <c r="AT40" s="5"/>
-      <c r="AU40" s="5"/>
-      <c r="AV40" s="5"/>
-      <c r="AW40" s="5"/>
-      <c r="AX40" s="5"/>
-      <c r="AY40" s="5"/>
-      <c r="AZ40" s="5"/>
-      <c r="BA40" s="5"/>
+      <c r="AM40" s="35"/>
+      <c r="AN40" s="36"/>
+      <c r="AO40" s="36"/>
+      <c r="AP40" s="36"/>
+      <c r="AQ40" s="36"/>
+      <c r="AR40" s="36"/>
+      <c r="AS40" s="36"/>
+      <c r="AT40" s="36"/>
+      <c r="AU40" s="36"/>
+      <c r="AV40" s="36"/>
+      <c r="AW40" s="36"/>
+      <c r="AX40" s="36"/>
+      <c r="AY40" s="36"/>
+      <c r="AZ40" s="36"/>
+      <c r="BA40" s="37"/>
       <c r="BB40" s="5"/>
       <c r="BC40" s="5"/>
-      <c r="BD40" s="5"/>
-      <c r="BE40" s="5"/>
-      <c r="BF40" s="5"/>
-      <c r="BG40" s="7"/>
-      <c r="BH40" s="5"/>
-      <c r="BI40" s="8"/>
-      <c r="BJ40" s="5"/>
-      <c r="BK40" s="5"/>
-      <c r="BL40" s="5"/>
-      <c r="BM40" s="5"/>
-      <c r="BN40" s="5"/>
-      <c r="BO40" s="5"/>
-      <c r="BP40" s="5"/>
-      <c r="BQ40" s="5"/>
-      <c r="BR40" s="5"/>
+      <c r="BD40" s="35"/>
+      <c r="BE40" s="36"/>
+      <c r="BF40" s="36"/>
+      <c r="BG40" s="36"/>
+      <c r="BH40" s="36"/>
+      <c r="BI40" s="36"/>
+      <c r="BJ40" s="36"/>
+      <c r="BK40" s="36"/>
+      <c r="BL40" s="36"/>
+      <c r="BM40" s="36"/>
+      <c r="BN40" s="36"/>
+      <c r="BO40" s="36"/>
+      <c r="BP40" s="36"/>
+      <c r="BQ40" s="36"/>
+      <c r="BR40" s="37"/>
       <c r="BS40" s="5"/>
       <c r="BT40" s="6"/>
     </row>
@@ -4797,38 +4839,38 @@
       <c r="AJ41" s="6"/>
       <c r="AK41" s="4"/>
       <c r="AL41" s="7"/>
-      <c r="AM41" s="8"/>
-      <c r="AN41" s="5"/>
-      <c r="AO41" s="5"/>
-      <c r="AP41" s="5"/>
-      <c r="AQ41" s="5"/>
-      <c r="AR41" s="5"/>
-      <c r="AS41" s="5"/>
-      <c r="AT41" s="5"/>
-      <c r="AU41" s="5"/>
-      <c r="AV41" s="5"/>
-      <c r="AW41" s="5"/>
-      <c r="AX41" s="5"/>
-      <c r="AY41" s="5"/>
-      <c r="AZ41" s="5"/>
-      <c r="BA41" s="5"/>
+      <c r="AM41" s="35"/>
+      <c r="AN41" s="36"/>
+      <c r="AO41" s="36"/>
+      <c r="AP41" s="36"/>
+      <c r="AQ41" s="36"/>
+      <c r="AR41" s="36"/>
+      <c r="AS41" s="36"/>
+      <c r="AT41" s="36"/>
+      <c r="AU41" s="36"/>
+      <c r="AV41" s="36"/>
+      <c r="AW41" s="36"/>
+      <c r="AX41" s="36"/>
+      <c r="AY41" s="36"/>
+      <c r="AZ41" s="36"/>
+      <c r="BA41" s="37"/>
       <c r="BB41" s="5"/>
       <c r="BC41" s="5"/>
-      <c r="BD41" s="5"/>
-      <c r="BE41" s="5"/>
-      <c r="BF41" s="5"/>
-      <c r="BG41" s="7"/>
-      <c r="BH41" s="5"/>
-      <c r="BI41" s="8"/>
-      <c r="BJ41" s="5"/>
-      <c r="BK41" s="5"/>
-      <c r="BL41" s="5"/>
-      <c r="BM41" s="5"/>
-      <c r="BN41" s="5"/>
-      <c r="BO41" s="5"/>
-      <c r="BP41" s="5"/>
-      <c r="BQ41" s="5"/>
-      <c r="BR41" s="5"/>
+      <c r="BD41" s="35"/>
+      <c r="BE41" s="36"/>
+      <c r="BF41" s="36"/>
+      <c r="BG41" s="36"/>
+      <c r="BH41" s="36"/>
+      <c r="BI41" s="36"/>
+      <c r="BJ41" s="36"/>
+      <c r="BK41" s="36"/>
+      <c r="BL41" s="36"/>
+      <c r="BM41" s="36"/>
+      <c r="BN41" s="36"/>
+      <c r="BO41" s="36"/>
+      <c r="BP41" s="36"/>
+      <c r="BQ41" s="36"/>
+      <c r="BR41" s="37"/>
       <c r="BS41" s="5"/>
       <c r="BT41" s="6"/>
     </row>
@@ -4871,38 +4913,38 @@
       <c r="AJ42" s="6"/>
       <c r="AK42" s="4"/>
       <c r="AL42" s="7"/>
-      <c r="AM42" s="8"/>
-      <c r="AN42" s="5"/>
-      <c r="AO42" s="5"/>
-      <c r="AP42" s="5"/>
-      <c r="AQ42" s="5"/>
-      <c r="AR42" s="5"/>
-      <c r="AS42" s="5"/>
-      <c r="AT42" s="5"/>
-      <c r="AU42" s="5"/>
-      <c r="AV42" s="5"/>
-      <c r="AW42" s="5"/>
-      <c r="AX42" s="5"/>
-      <c r="AY42" s="5"/>
-      <c r="AZ42" s="5"/>
-      <c r="BA42" s="5"/>
+      <c r="AM42" s="38"/>
+      <c r="AN42" s="39"/>
+      <c r="AO42" s="39"/>
+      <c r="AP42" s="39"/>
+      <c r="AQ42" s="39"/>
+      <c r="AR42" s="39"/>
+      <c r="AS42" s="39"/>
+      <c r="AT42" s="39"/>
+      <c r="AU42" s="39"/>
+      <c r="AV42" s="39"/>
+      <c r="AW42" s="39"/>
+      <c r="AX42" s="39"/>
+      <c r="AY42" s="39"/>
+      <c r="AZ42" s="39"/>
+      <c r="BA42" s="40"/>
       <c r="BB42" s="5"/>
       <c r="BC42" s="5"/>
-      <c r="BD42" s="5"/>
-      <c r="BE42" s="5"/>
-      <c r="BF42" s="5"/>
-      <c r="BG42" s="7"/>
-      <c r="BH42" s="5"/>
-      <c r="BI42" s="8"/>
-      <c r="BJ42" s="5"/>
-      <c r="BK42" s="5"/>
-      <c r="BL42" s="5"/>
-      <c r="BM42" s="5"/>
-      <c r="BN42" s="5"/>
-      <c r="BO42" s="5"/>
-      <c r="BP42" s="5"/>
-      <c r="BQ42" s="5"/>
-      <c r="BR42" s="5"/>
+      <c r="BD42" s="38"/>
+      <c r="BE42" s="39"/>
+      <c r="BF42" s="39"/>
+      <c r="BG42" s="39"/>
+      <c r="BH42" s="39"/>
+      <c r="BI42" s="39"/>
+      <c r="BJ42" s="39"/>
+      <c r="BK42" s="39"/>
+      <c r="BL42" s="39"/>
+      <c r="BM42" s="39"/>
+      <c r="BN42" s="39"/>
+      <c r="BO42" s="39"/>
+      <c r="BP42" s="39"/>
+      <c r="BQ42" s="39"/>
+      <c r="BR42" s="40"/>
       <c r="BS42" s="5"/>
       <c r="BT42" s="6"/>
     </row>
@@ -6284,40 +6326,40 @@
       <c r="AI61" s="42"/>
       <c r="AJ61" s="6"/>
       <c r="AK61" s="4"/>
-      <c r="AL61" s="7"/>
-      <c r="AM61" s="8"/>
-      <c r="AN61" s="5"/>
-      <c r="AO61" s="5"/>
-      <c r="AP61" s="5"/>
-      <c r="AQ61" s="5"/>
-      <c r="AR61" s="5"/>
-      <c r="AS61" s="5"/>
-      <c r="AT61" s="5"/>
-      <c r="AU61" s="5"/>
-      <c r="AV61" s="5"/>
-      <c r="AW61" s="5"/>
-      <c r="AX61" s="5"/>
-      <c r="AY61" s="5"/>
-      <c r="AZ61" s="5"/>
-      <c r="BA61" s="5"/>
-      <c r="BB61" s="5"/>
-      <c r="BC61" s="5"/>
-      <c r="BD61" s="5"/>
-      <c r="BE61" s="5"/>
-      <c r="BF61" s="5"/>
-      <c r="BG61" s="7"/>
-      <c r="BH61" s="5"/>
-      <c r="BI61" s="8"/>
-      <c r="BJ61" s="5"/>
-      <c r="BK61" s="5"/>
-      <c r="BL61" s="5"/>
-      <c r="BM61" s="5"/>
-      <c r="BN61" s="5"/>
-      <c r="BO61" s="5"/>
-      <c r="BP61" s="5"/>
-      <c r="BQ61" s="5"/>
-      <c r="BR61" s="5"/>
-      <c r="BS61" s="5"/>
+      <c r="AL61" s="18"/>
+      <c r="AM61" s="18"/>
+      <c r="AN61" s="18"/>
+      <c r="AO61" s="18"/>
+      <c r="AP61" s="18"/>
+      <c r="AQ61" s="18"/>
+      <c r="AR61" s="18"/>
+      <c r="AS61" s="18"/>
+      <c r="AT61" s="18"/>
+      <c r="AU61" s="18"/>
+      <c r="AV61" s="18"/>
+      <c r="AW61" s="18"/>
+      <c r="AX61" s="18"/>
+      <c r="AY61" s="18"/>
+      <c r="AZ61" s="18"/>
+      <c r="BA61" s="18"/>
+      <c r="BB61" s="18"/>
+      <c r="BC61" s="18"/>
+      <c r="BD61" s="18"/>
+      <c r="BE61" s="18"/>
+      <c r="BF61" s="18"/>
+      <c r="BG61" s="18"/>
+      <c r="BH61" s="18"/>
+      <c r="BI61" s="18"/>
+      <c r="BJ61" s="18"/>
+      <c r="BK61" s="18"/>
+      <c r="BL61" s="18"/>
+      <c r="BM61" s="18"/>
+      <c r="BN61" s="18"/>
+      <c r="BO61" s="18"/>
+      <c r="BP61" s="18"/>
+      <c r="BQ61" s="18"/>
+      <c r="BR61" s="18"/>
+      <c r="BS61" s="18"/>
       <c r="BT61" s="6"/>
     </row>
     <row r="62" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
@@ -6359,7 +6401,7 @@
       <c r="AJ62" s="6"/>
       <c r="AK62" s="4"/>
       <c r="AL62" s="7"/>
-      <c r="AM62" s="8"/>
+      <c r="AM62" s="7"/>
       <c r="AN62" s="5"/>
       <c r="AO62" s="5"/>
       <c r="AP62" s="5"/>
@@ -6431,44 +6473,44 @@
       <c r="AH63" s="5"/>
       <c r="AI63" s="5"/>
       <c r="AJ63" s="6"/>
-      <c r="AK63" s="4"/>
-      <c r="AL63" s="18"/>
-      <c r="AM63" s="18"/>
-      <c r="AN63" s="18"/>
-      <c r="AO63" s="18"/>
-      <c r="AP63" s="18"/>
-      <c r="AQ63" s="18"/>
-      <c r="AR63" s="18"/>
-      <c r="AS63" s="18"/>
-      <c r="AT63" s="18"/>
-      <c r="AU63" s="18"/>
-      <c r="AV63" s="18"/>
-      <c r="AW63" s="18"/>
-      <c r="AX63" s="18"/>
-      <c r="AY63" s="18"/>
-      <c r="AZ63" s="18"/>
-      <c r="BA63" s="18"/>
-      <c r="BB63" s="18"/>
-      <c r="BC63" s="18"/>
-      <c r="BD63" s="18"/>
-      <c r="BE63" s="18"/>
-      <c r="BF63" s="18"/>
-      <c r="BG63" s="18"/>
-      <c r="BH63" s="18"/>
-      <c r="BI63" s="18"/>
-      <c r="BJ63" s="18"/>
-      <c r="BK63" s="18"/>
-      <c r="BL63" s="18"/>
-      <c r="BM63" s="18"/>
-      <c r="BN63" s="18"/>
-      <c r="BO63" s="18"/>
-      <c r="BP63" s="18"/>
-      <c r="BQ63" s="18"/>
-      <c r="BR63" s="18"/>
-      <c r="BS63" s="18"/>
-      <c r="BT63" s="6"/>
+      <c r="AK63" s="9"/>
+      <c r="AL63" s="10"/>
+      <c r="AM63" s="10"/>
+      <c r="AN63" s="10"/>
+      <c r="AO63" s="15"/>
+      <c r="AP63" s="15"/>
+      <c r="AQ63" s="15"/>
+      <c r="AR63" s="15"/>
+      <c r="AS63" s="15"/>
+      <c r="AT63" s="15"/>
+      <c r="AU63" s="15"/>
+      <c r="AV63" s="15"/>
+      <c r="AW63" s="15"/>
+      <c r="AX63" s="15"/>
+      <c r="AY63" s="11"/>
+      <c r="AZ63" s="11"/>
+      <c r="BA63" s="11"/>
+      <c r="BB63" s="11"/>
+      <c r="BC63" s="11"/>
+      <c r="BD63" s="11"/>
+      <c r="BE63" s="11"/>
+      <c r="BF63" s="11"/>
+      <c r="BG63" s="11"/>
+      <c r="BH63" s="11"/>
+      <c r="BI63" s="11"/>
+      <c r="BJ63" s="11"/>
+      <c r="BK63" s="11"/>
+      <c r="BL63" s="11"/>
+      <c r="BM63" s="11"/>
+      <c r="BN63" s="11"/>
+      <c r="BO63" s="11"/>
+      <c r="BP63" s="11"/>
+      <c r="BQ63" s="11"/>
+      <c r="BR63" s="11"/>
+      <c r="BS63" s="11"/>
+      <c r="BT63" s="12"/>
     </row>
-    <row r="64" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:72" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7"/>
@@ -6505,44 +6547,48 @@
       <c r="AH64" s="5"/>
       <c r="AI64" s="5"/>
       <c r="AJ64" s="6"/>
-      <c r="AK64" s="4"/>
-      <c r="AL64" s="7"/>
-      <c r="AM64" s="7"/>
-      <c r="AN64" s="5"/>
-      <c r="AO64" s="5"/>
-      <c r="AP64" s="5"/>
-      <c r="AQ64" s="5"/>
-      <c r="AR64" s="5"/>
-      <c r="AS64" s="5"/>
-      <c r="AT64" s="5"/>
-      <c r="AU64" s="5"/>
-      <c r="AV64" s="5"/>
-      <c r="AW64" s="5"/>
-      <c r="AX64" s="5"/>
-      <c r="AY64" s="5"/>
-      <c r="AZ64" s="5"/>
-      <c r="BA64" s="5"/>
-      <c r="BB64" s="5"/>
-      <c r="BC64" s="5"/>
-      <c r="BD64" s="5"/>
-      <c r="BE64" s="5"/>
-      <c r="BF64" s="5"/>
-      <c r="BG64" s="7"/>
-      <c r="BH64" s="5"/>
-      <c r="BI64" s="8"/>
-      <c r="BJ64" s="5"/>
-      <c r="BK64" s="5"/>
-      <c r="BL64" s="5"/>
-      <c r="BM64" s="5"/>
-      <c r="BN64" s="5"/>
-      <c r="BO64" s="5"/>
-      <c r="BP64" s="5"/>
-      <c r="BQ64" s="5"/>
-      <c r="BR64" s="5"/>
-      <c r="BS64" s="5"/>
-      <c r="BT64" s="6"/>
+      <c r="AK64" s="52" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL64" s="53"/>
+      <c r="AM64" s="53"/>
+      <c r="AN64" s="53"/>
+      <c r="AO64" s="53"/>
+      <c r="AP64" s="53"/>
+      <c r="AQ64" s="53"/>
+      <c r="AR64" s="53"/>
+      <c r="AS64" s="53"/>
+      <c r="AT64" s="53"/>
+      <c r="AU64" s="53"/>
+      <c r="AV64" s="53"/>
+      <c r="AW64" s="53"/>
+      <c r="AX64" s="53"/>
+      <c r="AY64" s="53"/>
+      <c r="AZ64" s="53"/>
+      <c r="BA64" s="53"/>
+      <c r="BB64" s="53"/>
+      <c r="BC64" s="53"/>
+      <c r="BD64" s="53"/>
+      <c r="BE64" s="53"/>
+      <c r="BF64" s="53"/>
+      <c r="BG64" s="53"/>
+      <c r="BH64" s="53"/>
+      <c r="BI64" s="53"/>
+      <c r="BJ64" s="53"/>
+      <c r="BK64" s="53"/>
+      <c r="BL64" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="BM64" s="55"/>
+      <c r="BN64" s="55"/>
+      <c r="BO64" s="55"/>
+      <c r="BP64" s="55"/>
+      <c r="BQ64" s="55"/>
+      <c r="BR64" s="55"/>
+      <c r="BS64" s="55"/>
+      <c r="BT64" s="56"/>
     </row>
-    <row r="65" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:72" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A65" s="4"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7"/>
@@ -6579,44 +6625,44 @@
       <c r="AH65" s="5"/>
       <c r="AI65" s="5"/>
       <c r="AJ65" s="6"/>
-      <c r="AK65" s="9"/>
-      <c r="AL65" s="10"/>
-      <c r="AM65" s="10"/>
-      <c r="AN65" s="10"/>
-      <c r="AO65" s="15"/>
-      <c r="AP65" s="15"/>
-      <c r="AQ65" s="15"/>
-      <c r="AR65" s="15"/>
-      <c r="AS65" s="15"/>
-      <c r="AT65" s="15"/>
-      <c r="AU65" s="15"/>
-      <c r="AV65" s="15"/>
-      <c r="AW65" s="15"/>
-      <c r="AX65" s="15"/>
-      <c r="AY65" s="11"/>
-      <c r="AZ65" s="11"/>
-      <c r="BA65" s="11"/>
-      <c r="BB65" s="11"/>
-      <c r="BC65" s="11"/>
-      <c r="BD65" s="11"/>
-      <c r="BE65" s="11"/>
-      <c r="BF65" s="11"/>
-      <c r="BG65" s="11"/>
-      <c r="BH65" s="11"/>
-      <c r="BI65" s="11"/>
-      <c r="BJ65" s="11"/>
-      <c r="BK65" s="11"/>
-      <c r="BL65" s="11"/>
-      <c r="BM65" s="11"/>
-      <c r="BN65" s="11"/>
-      <c r="BO65" s="11"/>
-      <c r="BP65" s="11"/>
-      <c r="BQ65" s="11"/>
-      <c r="BR65" s="11"/>
-      <c r="BS65" s="11"/>
-      <c r="BT65" s="12"/>
+      <c r="AK65" s="48"/>
+      <c r="AL65" s="49"/>
+      <c r="AM65" s="49"/>
+      <c r="AN65" s="49"/>
+      <c r="AO65" s="49"/>
+      <c r="AP65" s="49"/>
+      <c r="AQ65" s="49"/>
+      <c r="AR65" s="49"/>
+      <c r="AS65" s="49"/>
+      <c r="AT65" s="49"/>
+      <c r="AU65" s="49"/>
+      <c r="AV65" s="49"/>
+      <c r="AW65" s="49"/>
+      <c r="AX65" s="49"/>
+      <c r="AY65" s="49"/>
+      <c r="AZ65" s="49"/>
+      <c r="BA65" s="49"/>
+      <c r="BB65" s="49"/>
+      <c r="BC65" s="49"/>
+      <c r="BD65" s="49"/>
+      <c r="BE65" s="49"/>
+      <c r="BF65" s="49"/>
+      <c r="BG65" s="49"/>
+      <c r="BH65" s="49"/>
+      <c r="BI65" s="49"/>
+      <c r="BJ65" s="49"/>
+      <c r="BK65" s="49"/>
+      <c r="BL65" s="49"/>
+      <c r="BM65" s="49"/>
+      <c r="BN65" s="49"/>
+      <c r="BO65" s="49"/>
+      <c r="BP65" s="49"/>
+      <c r="BQ65" s="49"/>
+      <c r="BR65" s="49"/>
+      <c r="BS65" s="49"/>
+      <c r="BT65" s="57"/>
     </row>
-    <row r="66" spans="1:72" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="4"/>
       <c r="B66" s="7"/>
       <c r="C66" s="7"/>
@@ -6653,48 +6699,44 @@
       <c r="AH66" s="5"/>
       <c r="AI66" s="5"/>
       <c r="AJ66" s="6"/>
-      <c r="AK66" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="AL66" s="53"/>
-      <c r="AM66" s="53"/>
-      <c r="AN66" s="53"/>
-      <c r="AO66" s="53"/>
-      <c r="AP66" s="53"/>
-      <c r="AQ66" s="53"/>
-      <c r="AR66" s="53"/>
-      <c r="AS66" s="53"/>
-      <c r="AT66" s="53"/>
-      <c r="AU66" s="53"/>
-      <c r="AV66" s="53"/>
-      <c r="AW66" s="53"/>
-      <c r="AX66" s="53"/>
-      <c r="AY66" s="53"/>
-      <c r="AZ66" s="53"/>
-      <c r="BA66" s="53"/>
-      <c r="BB66" s="53"/>
-      <c r="BC66" s="53"/>
-      <c r="BD66" s="53"/>
-      <c r="BE66" s="53"/>
-      <c r="BF66" s="53"/>
-      <c r="BG66" s="53"/>
-      <c r="BH66" s="53"/>
-      <c r="BI66" s="53"/>
-      <c r="BJ66" s="53"/>
-      <c r="BK66" s="53"/>
-      <c r="BL66" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="BM66" s="55"/>
-      <c r="BN66" s="55"/>
-      <c r="BO66" s="55"/>
-      <c r="BP66" s="55"/>
-      <c r="BQ66" s="55"/>
-      <c r="BR66" s="55"/>
-      <c r="BS66" s="55"/>
-      <c r="BT66" s="56"/>
+      <c r="AK66" s="48"/>
+      <c r="AL66" s="49"/>
+      <c r="AM66" s="49"/>
+      <c r="AN66" s="49"/>
+      <c r="AO66" s="49"/>
+      <c r="AP66" s="49"/>
+      <c r="AQ66" s="49"/>
+      <c r="AR66" s="49"/>
+      <c r="AS66" s="49"/>
+      <c r="AT66" s="49"/>
+      <c r="AU66" s="50"/>
+      <c r="AV66" s="50"/>
+      <c r="AW66" s="50"/>
+      <c r="AX66" s="50"/>
+      <c r="AY66" s="50"/>
+      <c r="AZ66" s="50"/>
+      <c r="BA66" s="50"/>
+      <c r="BB66" s="50"/>
+      <c r="BC66" s="50"/>
+      <c r="BD66" s="50"/>
+      <c r="BE66" s="49"/>
+      <c r="BF66" s="49"/>
+      <c r="BG66" s="49"/>
+      <c r="BH66" s="49"/>
+      <c r="BI66" s="50"/>
+      <c r="BJ66" s="50"/>
+      <c r="BK66" s="50"/>
+      <c r="BL66" s="50"/>
+      <c r="BM66" s="50"/>
+      <c r="BN66" s="50"/>
+      <c r="BO66" s="50"/>
+      <c r="BP66" s="50"/>
+      <c r="BQ66" s="50"/>
+      <c r="BR66" s="50"/>
+      <c r="BS66" s="50"/>
+      <c r="BT66" s="51"/>
     </row>
-    <row r="67" spans="1:72" ht="18" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:72" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A67" s="21"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -6731,122 +6773,50 @@
       <c r="AH67" s="23"/>
       <c r="AI67" s="23"/>
       <c r="AJ67" s="25"/>
-      <c r="AK67" s="48"/>
-      <c r="AL67" s="49"/>
-      <c r="AM67" s="49"/>
-      <c r="AN67" s="49"/>
-      <c r="AO67" s="49"/>
-      <c r="AP67" s="49"/>
-      <c r="AQ67" s="49"/>
-      <c r="AR67" s="49"/>
-      <c r="AS67" s="49"/>
-      <c r="AT67" s="49"/>
-      <c r="AU67" s="49"/>
-      <c r="AV67" s="49"/>
-      <c r="AW67" s="49"/>
-      <c r="AX67" s="49"/>
-      <c r="AY67" s="49"/>
-      <c r="AZ67" s="49"/>
-      <c r="BA67" s="49"/>
-      <c r="BB67" s="49"/>
-      <c r="BC67" s="49"/>
-      <c r="BD67" s="49"/>
-      <c r="BE67" s="49"/>
-      <c r="BF67" s="49"/>
-      <c r="BG67" s="49"/>
-      <c r="BH67" s="49"/>
-      <c r="BI67" s="49"/>
-      <c r="BJ67" s="49"/>
-      <c r="BK67" s="49"/>
-      <c r="BL67" s="49"/>
-      <c r="BM67" s="49"/>
-      <c r="BN67" s="49"/>
-      <c r="BO67" s="49"/>
-      <c r="BP67" s="49"/>
-      <c r="BQ67" s="49"/>
-      <c r="BR67" s="49"/>
-      <c r="BS67" s="49"/>
-      <c r="BT67" s="57"/>
-    </row>
-    <row r="68" spans="1:72" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="AK68" s="48"/>
-      <c r="AL68" s="49"/>
-      <c r="AM68" s="49"/>
-      <c r="AN68" s="49"/>
-      <c r="AO68" s="49"/>
-      <c r="AP68" s="49"/>
-      <c r="AQ68" s="49"/>
-      <c r="AR68" s="49"/>
-      <c r="AS68" s="49"/>
-      <c r="AT68" s="49"/>
-      <c r="AU68" s="50"/>
-      <c r="AV68" s="50"/>
-      <c r="AW68" s="50"/>
-      <c r="AX68" s="50"/>
-      <c r="AY68" s="50"/>
-      <c r="AZ68" s="50"/>
-      <c r="BA68" s="50"/>
-      <c r="BB68" s="50"/>
-      <c r="BC68" s="50"/>
-      <c r="BD68" s="50"/>
-      <c r="BE68" s="49"/>
-      <c r="BF68" s="49"/>
-      <c r="BG68" s="49"/>
-      <c r="BH68" s="49"/>
-      <c r="BI68" s="50"/>
-      <c r="BJ68" s="50"/>
-      <c r="BK68" s="50"/>
-      <c r="BL68" s="50"/>
-      <c r="BM68" s="50"/>
-      <c r="BN68" s="50"/>
-      <c r="BO68" s="50"/>
-      <c r="BP68" s="50"/>
-      <c r="BQ68" s="50"/>
-      <c r="BR68" s="50"/>
-      <c r="BS68" s="50"/>
-      <c r="BT68" s="51"/>
-    </row>
-    <row r="69" spans="1:72" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="AK69" s="43"/>
-      <c r="AL69" s="44"/>
-      <c r="AM69" s="44"/>
-      <c r="AN69" s="44"/>
-      <c r="AO69" s="44"/>
-      <c r="AP69" s="44"/>
-      <c r="AQ69" s="44"/>
-      <c r="AR69" s="44"/>
-      <c r="AS69" s="44"/>
-      <c r="AT69" s="44"/>
-      <c r="AU69" s="45"/>
-      <c r="AV69" s="45"/>
-      <c r="AW69" s="45"/>
-      <c r="AX69" s="45"/>
-      <c r="AY69" s="45"/>
-      <c r="AZ69" s="45"/>
-      <c r="BA69" s="45"/>
-      <c r="BB69" s="45"/>
-      <c r="BC69" s="45"/>
-      <c r="BD69" s="45"/>
-      <c r="BE69" s="44"/>
-      <c r="BF69" s="44"/>
-      <c r="BG69" s="44"/>
-      <c r="BH69" s="44"/>
-      <c r="BI69" s="45"/>
-      <c r="BJ69" s="45"/>
-      <c r="BK69" s="45"/>
-      <c r="BL69" s="46"/>
-      <c r="BM69" s="46"/>
-      <c r="BN69" s="46"/>
-      <c r="BO69" s="46"/>
-      <c r="BP69" s="46"/>
-      <c r="BQ69" s="46"/>
-      <c r="BR69" s="46"/>
-      <c r="BS69" s="46"/>
-      <c r="BT69" s="47"/>
+      <c r="AK67" s="43"/>
+      <c r="AL67" s="44"/>
+      <c r="AM67" s="44"/>
+      <c r="AN67" s="44"/>
+      <c r="AO67" s="44"/>
+      <c r="AP67" s="44"/>
+      <c r="AQ67" s="44"/>
+      <c r="AR67" s="44"/>
+      <c r="AS67" s="44"/>
+      <c r="AT67" s="44"/>
+      <c r="AU67" s="45"/>
+      <c r="AV67" s="45"/>
+      <c r="AW67" s="45"/>
+      <c r="AX67" s="45"/>
+      <c r="AY67" s="45"/>
+      <c r="AZ67" s="45"/>
+      <c r="BA67" s="45"/>
+      <c r="BB67" s="45"/>
+      <c r="BC67" s="45"/>
+      <c r="BD67" s="45"/>
+      <c r="BE67" s="44"/>
+      <c r="BF67" s="44"/>
+      <c r="BG67" s="44"/>
+      <c r="BH67" s="44"/>
+      <c r="BI67" s="45"/>
+      <c r="BJ67" s="45"/>
+      <c r="BK67" s="45"/>
+      <c r="BL67" s="46"/>
+      <c r="BM67" s="46"/>
+      <c r="BN67" s="46"/>
+      <c r="BO67" s="46"/>
+      <c r="BP67" s="46"/>
+      <c r="BQ67" s="46"/>
+      <c r="BR67" s="46"/>
+      <c r="BS67" s="46"/>
+      <c r="BT67" s="47"/>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="61">
+  <mergeCells count="65">
+    <mergeCell ref="AM26:BA27"/>
+    <mergeCell ref="BD26:BR27"/>
+    <mergeCell ref="AM28:BA42"/>
+    <mergeCell ref="BD28:BR42"/>
     <mergeCell ref="F1:J2"/>
     <mergeCell ref="K1:P2"/>
     <mergeCell ref="AE2:AJ2"/>
@@ -6885,23 +6855,23 @@
     <mergeCell ref="AF9:AJ9"/>
     <mergeCell ref="AF7:AJ7"/>
     <mergeCell ref="A5:D6"/>
-    <mergeCell ref="AK66:BK66"/>
+    <mergeCell ref="AK64:BK64"/>
+    <mergeCell ref="BL64:BT64"/>
+    <mergeCell ref="AK65:AT65"/>
+    <mergeCell ref="AU65:BD65"/>
+    <mergeCell ref="BE65:BH65"/>
+    <mergeCell ref="BI65:BK65"/>
+    <mergeCell ref="BL65:BT65"/>
+    <mergeCell ref="AK66:AT66"/>
+    <mergeCell ref="AU66:BD66"/>
+    <mergeCell ref="BE66:BH66"/>
+    <mergeCell ref="BI66:BK66"/>
     <mergeCell ref="BL66:BT66"/>
     <mergeCell ref="AK67:AT67"/>
     <mergeCell ref="AU67:BD67"/>
     <mergeCell ref="BE67:BH67"/>
     <mergeCell ref="BI67:BK67"/>
     <mergeCell ref="BL67:BT67"/>
-    <mergeCell ref="AK68:AT68"/>
-    <mergeCell ref="AU68:BD68"/>
-    <mergeCell ref="BE68:BH68"/>
-    <mergeCell ref="BI68:BK68"/>
-    <mergeCell ref="BL68:BT68"/>
-    <mergeCell ref="AK69:AT69"/>
-    <mergeCell ref="AU69:BD69"/>
-    <mergeCell ref="BE69:BH69"/>
-    <mergeCell ref="BI69:BK69"/>
-    <mergeCell ref="BL69:BT69"/>
     <mergeCell ref="AK3:BT4"/>
     <mergeCell ref="AM10:BA24"/>
     <mergeCell ref="AM8:BA9"/>
